--- a/data/trans_bre/P38C-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Estudios-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,17</t>
+          <t>1,55; 7,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,91</t>
+          <t>0,33; 7,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,28</t>
+          <t>1,73; 8,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 9,17</t>
+          <t>0,36; 8,82</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,93</t>
+          <t>4,15; 8,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 40,71</t>
+          <t>3,38; 34,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,37</t>
+          <t>5,17; 11,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 90,21</t>
+          <t>4,27; 67,39</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 7,46</t>
+          <t>-1,82; 7,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,53</t>
+          <t>2,3; 11,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 9,68</t>
+          <t>-2,18; 9,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 16,1</t>
+          <t>2,73; 14,3</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,76</t>
+          <t>4,14; 7,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 31,47</t>
+          <t>4,32; 29,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 9,65</t>
+          <t>5,05; 9,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 55,6</t>
+          <t>5,42; 51,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38C-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P38C-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>6,76</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,39</t>
+          <t>1,82; 7,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,56</t>
+          <t>3,7; 10,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,59</t>
+          <t>2,03; 8,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 8,82</t>
+          <t>4,17; 12,87</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,05</t>
+          <t>6,76</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,97</t>
+          <t>4,1; 8,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 34,73</t>
+          <t>3,99; 9,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,56</t>
+          <t>5,07; 11,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 67,39</t>
+          <t>5,1; 13,35</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 7,68</t>
+          <t>-1,27; 7,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 11,18</t>
+          <t>1,78; 9,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,94</t>
+          <t>-1,54; 10,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,3</t>
+          <t>2,07; 12,37</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,78</t>
+          <t>3,97; 7,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 29,61</t>
+          <t>5,02; 9,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,75</t>
+          <t>4,79; 9,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 51,85</t>
+          <t>6,2; 11,79</t>
         </is>
       </c>
     </row>
